--- a/TARIFAS LUZ Y GAS JUNIO 2026.xlsx
+++ b/TARIFAS LUZ Y GAS JUNIO 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Propietario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{491B4BAF-82C7-4DB2-8A3F-BDF87200F02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF71CFD6-888D-4BDE-909D-948B4739B78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8459886D-EEBB-46B1-835F-7F67F623B25F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>LUZ</t>
   </si>
@@ -123,13 +123,10 @@
     <t>GANA (*)</t>
   </si>
   <si>
-    <t>GASTOS DE GESTION</t>
-  </si>
-  <si>
-    <t>(*) INDEXADO</t>
-  </si>
-  <si>
     <t>IBERDROLA</t>
+  </si>
+  <si>
+    <t>GASTOS DE GESTION (*) INDEXADO</t>
   </si>
 </sst>
 </file>
@@ -208,13 +205,7 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -223,15 +214,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -552,52 +549,52 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.77734375" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" customWidth="1"/>
+    <col min="6" max="6" width="34.21875" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -605,17 +602,17 @@
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>0.112</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5">
         <v>0.12303</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>3.7337000000000002E-2</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>0.06</v>
       </c>
     </row>
@@ -623,17 +620,17 @@
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>0.11899999999999999</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5">
         <v>8.9434E-2</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>8.9434E-2</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>0.06</v>
       </c>
     </row>
@@ -641,19 +638,19 @@
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>0.127</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>0.123</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>9.3665999999999999E-2</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>9.3665999999999999E-2</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>0.06</v>
       </c>
     </row>
@@ -661,19 +658,19 @@
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>0.127</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>0.123</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>9.3665999999999999E-2</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>9.3665999999999999E-2</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>0.06</v>
       </c>
       <c r="G7" t="s">
@@ -684,19 +681,19 @@
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>0.124</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>0.11700000000000001</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>0.11915100000000001</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>0.06</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>0.05</v>
       </c>
       <c r="G8" t="s">
@@ -707,17 +704,17 @@
       <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>0.115</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="5">
         <v>0.06</v>
       </c>
     </row>
@@ -725,19 +722,19 @@
       <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>0.13200000000000001</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>0.129</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <v>0.06</v>
       </c>
     </row>
@@ -745,17 +742,17 @@
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>0.11899999999999999</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <v>0.06</v>
       </c>
       <c r="G11" t="s">
@@ -766,17 +763,17 @@
       <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <v>0.13400000000000001</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5">
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G12" t="s">
@@ -787,180 +784,180 @@
       <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>0.124</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="11"/>
+      <c r="B15" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3" t="s">
+      <c r="C15" s="10"/>
+      <c r="D15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="3"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="7">
         <v>7.9533000000000006E-2</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="7">
         <v>7.7434000000000003E-2</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="8">
         <v>5.1508089999999997</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="8">
         <v>9.1498019999999993</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="5">
         <v>6.0699999999999997E-2</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>5.8599999999999999E-2</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="8">
         <v>3.93</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="8">
         <v>8.11</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="5">
         <v>8.2699999999999996E-2</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>7.9200000000000007E-2</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="8">
         <v>7.181</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="8">
         <v>14.6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="10">
+        <v>28</v>
+      </c>
+      <c r="B20" s="7">
         <v>9.5727999999999994E-2</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="7">
         <v>9.0965000000000004E-2</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="8">
         <v>6.25</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="8">
         <v>11.18</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="5">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="8">
         <v>6.03</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="8">
         <v>11.3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="5">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="5">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="8">
         <v>9.5</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="8">
         <v>14.5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="5">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="5">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="8">
         <v>9.5</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="8">
         <v>14.5</v>
       </c>
     </row>
